--- a/data/trans_dic/IP04D$individual-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -521,8 +522,10 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -675,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,34; 25,82</t>
+          <t>12,26; 26,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 20,1</t>
+          <t>6,12; 20,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,26; 17,19</t>
+          <t>2,97; 16,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,7; 24,14</t>
+          <t>10,62; 23,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,05; 19,04</t>
+          <t>5,85; 18,99</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,18; 31,7</t>
+          <t>10,96; 31,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,1; 22,37</t>
+          <t>12,76; 21,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,2; 16,61</t>
+          <t>7,05; 16,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,68; 22,34</t>
+          <t>8,9; 22,55</t>
         </is>
       </c>
     </row>
@@ -785,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,67; 29,42</t>
+          <t>22,73; 29,07</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,42; 33,46</t>
+          <t>26,81; 33,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,12; 16,16</t>
+          <t>10,22; 16,27</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,54; 33,27</t>
+          <t>26,31; 33,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,18; 32,09</t>
+          <t>25,26; 31,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,65; 23,49</t>
+          <t>13,49; 23,79</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,77; 30,35</t>
+          <t>25,6; 30,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,25; 32,17</t>
+          <t>27,01; 31,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,9; 18,82</t>
+          <t>12,88; 18,87</t>
         </is>
       </c>
     </row>
@@ -895,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,33; 46,82</t>
+          <t>33,45; 46,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,66; 50,19</t>
+          <t>37,69; 50,03</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,11; 34,37</t>
+          <t>21,97; 34,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,83; 50,99</t>
+          <t>38,57; 51,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>29,52; 41,33</t>
+          <t>30,17; 41,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,09; 36,61</t>
+          <t>24,85; 37,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>37,86; 46,9</t>
+          <t>38,12; 47,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>34,91; 43,76</t>
+          <t>35,11; 43,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,01; 33,7</t>
+          <t>24,97; 34,3</t>
         </is>
       </c>
     </row>
@@ -1005,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,48; 30,94</t>
+          <t>25,65; 31,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,96; 34,57</t>
+          <t>28,87; 34,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,17; 18,71</t>
+          <t>13,11; 18,54</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29,0; 34,43</t>
+          <t>28,93; 34,34</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,08; 31,18</t>
+          <t>25,72; 31,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,69; 24,76</t>
+          <t>17,63; 25,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,05; 32,11</t>
+          <t>28,06; 31,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,25; 32,25</t>
+          <t>28,46; 32,34</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,32; 21,06</t>
+          <t>16,4; 21,35</t>
         </is>
       </c>
     </row>
@@ -1069,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>nan (tasa de respuesta: 99,64%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>17061</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6974</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>12556</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31362</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>14483</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>16882</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>11322; 24099</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>3594; 11762</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1626; 8967</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9157; 20405</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>4016; 13029</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6796; 19669</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>22783; 39019</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>8974; 21392</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>10386; 26311</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>383</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>115935</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>141201</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>60225</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>146444</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>139042</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>87852</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>262380</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>280242</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>148077</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>102087; 130576</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>126201; 158013</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47084; 74924</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>129748; 163013</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>122787; 155482</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>69586; 122720</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>241255; 285388</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>258463; 303564</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>125745; 184275</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>66912</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74570</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>41463</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>77276</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65488</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>55908</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>144188</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>140058</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>97371</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>55801; 77273</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>64310; 85369</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>32642; 50512</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>66432; 88860</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>55903; 76715</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>45327; 68067</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>129258; 159452</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>124990; 153859</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>82626; 113525</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>629</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>648</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>199908</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>222745</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>106014</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>156315</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>437929</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>434784</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>262330</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>181701; 221031</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>202173; 242461</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>87022; 123086</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>217470; 258063</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>190319; 232392</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>134069; 191362</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>409648; 465813</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>409889; 465742</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>233500; 303995</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP04D$individual-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Estudios-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,26; 26,09</t>
+          <t>12,7; 25,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,12; 20,02</t>
+          <t>6,72; 20,02</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,97; 16,4</t>
+          <t>2,78; 17,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,62; 23,67</t>
+          <t>10,36; 23,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,85; 18,99</t>
+          <t>5,83; 19,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,96; 31,72</t>
+          <t>11,59; 32,4</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,76; 21,85</t>
+          <t>13,25; 22,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 16,8</t>
+          <t>7,58; 16,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,9; 22,55</t>
+          <t>8,84; 22,08</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,73; 29,07</t>
+          <t>22,71; 29,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,81; 33,56</t>
+          <t>26,64; 33,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,22; 16,27</t>
+          <t>9,95; 16,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,31; 33,05</t>
+          <t>26,43; 33,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,26; 31,99</t>
+          <t>25,48; 32,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,49; 23,79</t>
+          <t>13,63; 24,02</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,6; 30,29</t>
+          <t>25,64; 30,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>27,01; 31,72</t>
+          <t>26,86; 31,64</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,88; 18,87</t>
+          <t>12,78; 18,95</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,45; 46,32</t>
+          <t>33,41; 46,38</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,69; 50,03</t>
+          <t>37,51; 49,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>21,97; 34,0</t>
+          <t>22,09; 34,66</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,57; 51,59</t>
+          <t>38,23; 50,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,17; 41,4</t>
+          <t>30,0; 41,33</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,85; 37,32</t>
+          <t>24,8; 37,82</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,12; 47,03</t>
+          <t>38,0; 46,83</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,11; 43,23</t>
+          <t>35,63; 43,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>24,97; 34,3</t>
+          <t>25,35; 34,58</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,65; 31,21</t>
+          <t>25,4; 31,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>28,87; 34,63</t>
+          <t>29,0; 34,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,11; 18,54</t>
+          <t>13,17; 18,93</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,93; 34,34</t>
+          <t>28,84; 34,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,72; 31,4</t>
+          <t>26,14; 31,62</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,63; 25,17</t>
+          <t>17,7; 24,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>28,06; 31,91</t>
+          <t>27,87; 32,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,46; 32,34</t>
+          <t>28,13; 32,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,4; 21,35</t>
+          <t>16,33; 20,83</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11322; 24099</t>
+          <t>11727; 23878</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3594; 11762</t>
+          <t>3947; 11764</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1626; 8967</t>
+          <t>1521; 9313</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9157; 20405</t>
+          <t>8932; 20509</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>4016; 13029</t>
+          <t>3998; 13272</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6796; 19669</t>
+          <t>7186; 20087</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22783; 39019</t>
+          <t>23655; 40587</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8974; 21392</t>
+          <t>9651; 21194</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10386; 26311</t>
+          <t>10319; 25759</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>102087; 130576</t>
+          <t>101991; 131071</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>126201; 158013</t>
+          <t>125428; 156376</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>47084; 74924</t>
+          <t>45830; 74335</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129748; 163013</t>
+          <t>130325; 164286</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>122787; 155482</t>
+          <t>123851; 157937</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>69586; 122720</t>
+          <t>70336; 123898</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>241255; 285388</t>
+          <t>241641; 286775</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>258463; 303564</t>
+          <t>257028; 302741</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>125745; 184275</t>
+          <t>124791; 185046</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55801; 77273</t>
+          <t>55732; 77366</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64310; 85369</t>
+          <t>64009; 84826</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32642; 50512</t>
+          <t>32813; 51484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>66432; 88860</t>
+          <t>65836; 87396</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55903; 76715</t>
+          <t>55584; 76593</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45327; 68067</t>
+          <t>45228; 68981</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>129258; 159452</t>
+          <t>128840; 158762</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>124990; 153859</t>
+          <t>126811; 155986</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>82626; 113525</t>
+          <t>83882; 114450</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>181701; 221031</t>
+          <t>179896; 219776</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>202173; 242461</t>
+          <t>203027; 242223</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87022; 123086</t>
+          <t>87384; 125630</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>217470; 258063</t>
+          <t>216775; 260300</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>190319; 232392</t>
+          <t>193406; 234009</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>134069; 191362</t>
+          <t>134546; 189991</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>409648; 465813</t>
+          <t>406819; 467700</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>409889; 465742</t>
+          <t>405192; 463161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>233500; 303995</t>
+          <t>232574; 296681</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP04D$individual-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP04D$individual-Estudios-trans_dic.xlsx
@@ -524,20 +524,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>20,75%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>18,47%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,87%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,91%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>16,59%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,94%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,7; 25,85</t>
+          <t>10,7; 24,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,72; 20,02</t>
+          <t>6,05; 19,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,78; 17,03</t>
+          <t>11,42; 32,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 23,79</t>
+          <t>12,34; 25,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,83; 19,34</t>
+          <t>6,15; 20,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,59; 32,4</t>
+          <t>3,7; 19,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,25; 22,73</t>
+          <t>13,1; 22,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7,58; 16,64</t>
+          <t>7,2; 16,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 22,08</t>
+          <t>9,65; 23,76</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,69%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>28,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>16,86%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>25,81%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>29,99%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>13,08%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29,69%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>28,6%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,71; 29,18</t>
+          <t>26,54; 33,27</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>26,64; 33,22</t>
+          <t>25,18; 32,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 16,14</t>
+          <t>13,58; 22,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,43; 33,31</t>
+          <t>22,67; 29,42</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,48; 32,49</t>
+          <t>26,42; 33,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 24,02</t>
+          <t>11,37; 17,13</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,64; 30,43</t>
+          <t>25,77; 30,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>26,86; 31,64</t>
+          <t>27,25; 32,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>12,78; 18,95</t>
+          <t>13,34; 18,76</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>44,87%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>40,11%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>43,7%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>27,91%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>44,87%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>33,41; 46,38</t>
+          <t>38,83; 50,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37,51; 49,71</t>
+          <t>29,52; 41,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22,09; 34,66</t>
+          <t>24,39; 37,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38,23; 50,74</t>
+          <t>33,33; 46,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>30,0; 41,33</t>
+          <t>37,66; 50,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>24,8; 37,82</t>
+          <t>21,75; 34,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,0; 46,83</t>
+          <t>37,86; 46,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>35,63; 43,82</t>
+          <t>34,91; 43,76</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>25,35; 34,58</t>
+          <t>25,24; 33,8</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>31,67%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28,65%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>28,22%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>31,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>15,97%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>16,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,86%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,4; 31,03</t>
+          <t>29,0; 34,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29,0; 34,59</t>
+          <t>26,08; 31,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,17; 18,93</t>
+          <t>17,68; 24,62</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>28,84; 34,63</t>
+          <t>25,48; 30,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,14; 31,62</t>
+          <t>28,96; 34,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,7; 24,99</t>
+          <t>14,47; 19,46</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,87; 32,04</t>
+          <t>28,05; 32,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>28,13; 32,16</t>
+          <t>28,25; 32,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>16,33; 20,83</t>
+          <t>16,76; 21,12</t>
         </is>
       </c>
     </row>
@@ -1099,20 +1099,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>nan (tasa de respuesta: 99,64%)</t>
+          <t>Población que dispone de calefacción individual en su vivienda (tasa de respuesta: 99,64%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>14301</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>7509</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>11774</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>17061</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>6974</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>4326</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14301</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>7509</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16300</t>
         </is>
       </c>
     </row>
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11727; 23878</t>
+          <t>9220; 20805</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3947; 11764</t>
+          <t>4151; 13066</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1521; 9313</t>
+          <t>6479; 18334</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8932; 20509</t>
+          <t>11399; 23849</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3998; 13272</t>
+          <t>3616; 11810</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>7186; 20087</t>
+          <t>1732; 9156</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23655; 40587</t>
+          <t>23392; 39951</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9651; 21194</t>
+          <t>9172; 21154</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>10319; 25759</t>
+          <t>9992; 24586</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>218</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>87</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>213</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>146444</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>139042</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>80088</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>115935</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>141201</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>60225</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>146444</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>139042</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>87852</t>
+          <t>60714</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>148077</t>
+          <t>140802</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>101991; 131071</t>
+          <t>130873; 164082</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>125428; 156376</t>
+          <t>122406; 155984</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45830; 74335</t>
+          <t>64494; 109176</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>130325; 164286</t>
+          <t>101829; 132133</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>123851; 157937</t>
+          <t>124360; 157520</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>70336; 123898</t>
+          <t>49184; 74092</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>241641; 286775</t>
+          <t>242845; 286006</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>257028; 302741</t>
+          <t>260779; 307851</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>124791; 185046</t>
+          <t>121082; 170214</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>113</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>60</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>77276</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65488</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>52057</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>66912</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>74570</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>41463</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77276</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>65488</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55908</t>
+          <t>41121</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>97371</t>
+          <t>93178</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>55732; 77366</t>
+          <t>66874; 87821</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64009; 84826</t>
+          <t>54703; 76583</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32813; 51484</t>
+          <t>40846; 62356</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>65836; 87396</t>
+          <t>55601; 78105</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>55584; 76593</t>
+          <t>64265; 85639</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45228; 68981</t>
+          <t>32393; 50752</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>128840; 158762</t>
+          <t>128365; 159008</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>126811; 155986</t>
+          <t>124278; 155758</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>83882; 114450</t>
+          <t>79861; 106927</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>287</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>342</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>238021</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>212039</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>143920</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>199908</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>222745</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>106014</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>238021</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>212039</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>156315</t>
+          <t>106361</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>262330</t>
+          <t>250281</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>179896; 219776</t>
+          <t>217925; 258765</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>203027; 242223</t>
+          <t>193026; 230708</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>87384; 125630</t>
+          <t>123615; 172157</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>216775; 260300</t>
+          <t>180444; 219171</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>193406; 234009</t>
+          <t>202777; 242038</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>134546; 189991</t>
+          <t>90882; 122211</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>406819; 467700</t>
+          <t>409546; 468710</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>405192; 463161</t>
+          <t>406858; 464447</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>232574; 296681</t>
+          <t>222521; 280327</t>
         </is>
       </c>
     </row>
